--- a/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T15:55:45+00:00</t>
+    <t>2024-11-26T12:51:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T12:51:17+00:00</t>
+    <t>2024-11-26T14:12:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T14:12:54+00:00</t>
+    <t>2024-12-02T10:46:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3851" uniqueCount="548">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T10:46:43+00:00</t>
+    <t>2024-12-02T16:50:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -817,7 +817,7 @@
     <t>ValueSet.url</t>
   </si>
   <si>
-    <t>L'ANS est autorité sur les URLs de type https://mos.esante.gouv.fr/fhir/ValueSet/* et https://smt.esante.gouv.fr/fhir/ValueSet/*</t>
+    <t>URL au format https://smt.esante.gouv.fr/fhir/ValueSet/*</t>
   </si>
   <si>
     <t>An absolute URI that is used to identify this value set when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this value set is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the value set is stored on different servers.</t>
@@ -829,6 +829,10 @@
   </si>
   <si>
     <t>Allows the value set to be referenced by a single globally unique identifier.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ans-vs-url-regex:url matches smt regex {$this.matches('https:\/\/smt.esante.gouv.fr\/fhir\/ValueSet\/[a-z0-9]+(?:-[a-z0-9]+)*')}</t>
   </si>
   <si>
     <t>Definition.url</t>
@@ -5593,16 +5597,16 @@
         <v>75</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5610,10 +5614,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5636,19 +5640,19 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>75</v>
@@ -5697,7 +5701,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5715,21 +5719,21 @@
         <v>75</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5755,13 +5759,13 @@
         <v>99</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5811,7 +5815,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5829,10 +5833,10 @@
         <v>75</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5840,10 +5844,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5869,16 +5873,16 @@
         <v>99</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5927,7 +5931,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5936,7 +5940,7 @@
         <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>97</v>
@@ -5956,10 +5960,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5985,13 +5989,13 @@
         <v>99</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6041,7 +6045,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6059,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>75</v>
@@ -6070,10 +6074,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6099,13 +6103,13 @@
         <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6134,10 +6138,10 @@
         <v>151</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -6155,7 +6159,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6173,10 +6177,10 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -6184,10 +6188,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6210,19 +6214,19 @@
         <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -6271,7 +6275,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6289,10 +6293,10 @@
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6300,14 +6304,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6329,13 +6333,13 @@
         <v>225</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6385,7 +6389,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6403,10 +6407,10 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6414,14 +6418,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6443,16 +6447,16 @@
         <v>99</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6501,7 +6505,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6519,10 +6523,10 @@
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6530,10 +6534,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6556,16 +6560,16 @@
         <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6615,7 +6619,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6633,7 +6637,7 @@
         <v>75</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>75</v>
@@ -6644,14 +6648,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6670,16 +6674,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6729,7 +6733,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6747,7 +6751,7 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -6758,10 +6762,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6784,19 +6788,19 @@
         <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -6845,7 +6849,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6863,7 +6867,7 @@
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -6874,10 +6878,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6900,16 +6904,16 @@
         <v>85</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6938,10 +6942,10 @@
         <v>143</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6959,7 +6963,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6977,7 +6981,7 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
@@ -6988,10 +6992,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7014,16 +7018,16 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7073,7 +7077,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7102,10 +7106,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7128,16 +7132,16 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7187,7 +7191,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7205,25 +7209,25 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7242,19 +7246,19 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -7303,7 +7307,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7321,25 +7325,25 @@
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7358,13 +7362,13 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7415,7 +7419,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7444,10 +7448,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7556,10 +7560,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7670,14 +7674,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7699,10 +7703,10 @@
         <v>106</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>109</v>
@@ -7757,7 +7761,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7786,10 +7790,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7812,16 +7816,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7871,7 +7875,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7892,7 +7896,7 @@
         <v>75</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7900,10 +7904,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7926,16 +7930,16 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7985,7 +7989,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8014,10 +8018,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8040,16 +8044,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8099,7 +8103,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8111,7 +8115,7 @@
         <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8128,10 +8132,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8240,10 +8244,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8354,14 +8358,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8383,10 +8387,10 @@
         <v>106</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>109</v>
@@ -8441,7 +8445,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8470,10 +8474,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8499,13 +8503,13 @@
         <v>127</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8555,7 +8559,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8564,7 +8568,7 @@
         <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>97</v>
@@ -8584,10 +8588,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8613,13 +8617,13 @@
         <v>99</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8669,7 +8673,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8698,10 +8702,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8724,16 +8728,16 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8783,7 +8787,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8792,7 +8796,7 @@
         <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>97</v>
@@ -8812,10 +8816,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8924,10 +8928,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9038,14 +9042,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9067,10 +9071,10 @@
         <v>106</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>109</v>
@@ -9125,7 +9129,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9154,10 +9158,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9183,13 +9187,13 @@
         <v>167</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9239,7 +9243,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9268,10 +9272,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9297,13 +9301,13 @@
         <v>99</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9353,7 +9357,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9382,10 +9386,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9408,16 +9412,16 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9467,7 +9471,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9496,10 +9500,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9608,10 +9612,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9722,14 +9726,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9751,10 +9755,10 @@
         <v>106</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>109</v>
@@ -9809,7 +9813,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9838,10 +9842,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9867,13 +9871,13 @@
         <v>167</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9923,7 +9927,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -9952,10 +9956,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9981,13 +9985,13 @@
         <v>139</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10016,10 +10020,10 @@
         <v>143</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -10037,7 +10041,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10066,10 +10070,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10095,10 +10099,10 @@
         <v>99</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10149,7 +10153,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10178,10 +10182,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10204,16 +10208,16 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10263,7 +10267,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10272,7 +10276,7 @@
         <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>97</v>
@@ -10292,10 +10296,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10404,10 +10408,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10518,14 +10522,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10547,10 +10551,10 @@
         <v>106</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>109</v>
@@ -10605,7 +10609,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -10634,10 +10638,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10663,10 +10667,10 @@
         <v>167</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10717,7 +10721,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10746,10 +10750,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10775,13 +10779,13 @@
         <v>167</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10810,10 +10814,10 @@
         <v>151</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -10831,7 +10835,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10860,10 +10864,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10889,13 +10893,13 @@
         <v>99</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10945,7 +10949,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -10974,10 +10978,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11000,16 +11004,16 @@
         <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11059,7 +11063,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11068,7 +11072,7 @@
         <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>97</v>
@@ -11088,10 +11092,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11117,13 +11121,13 @@
         <v>77</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11173,7 +11177,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11182,7 +11186,7 @@
         <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>97</v>
@@ -11202,10 +11206,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11228,16 +11232,16 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11287,7 +11291,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11316,10 +11320,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11428,10 +11432,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11542,14 +11546,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -11571,10 +11575,10 @@
         <v>106</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>109</v>
@@ -11629,7 +11633,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -11658,10 +11662,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11687,13 +11691,13 @@
         <v>127</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11743,7 +11747,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -11772,10 +11776,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11801,13 +11805,13 @@
         <v>225</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11857,7 +11861,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -11886,10 +11890,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11912,16 +11916,16 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11971,7 +11975,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12000,10 +12004,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12026,23 +12030,23 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="R88" t="s" s="2">
         <v>75</v>
@@ -12087,7 +12091,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12116,10 +12120,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12142,16 +12146,16 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12201,7 +12205,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12230,10 +12234,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12342,10 +12346,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12456,14 +12460,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12485,10 +12489,10 @@
         <v>106</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>109</v>
@@ -12543,7 +12547,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -12572,10 +12576,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12601,13 +12605,13 @@
         <v>99</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12657,7 +12661,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12686,10 +12690,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12712,13 +12716,13 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12769,7 +12773,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -12798,10 +12802,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12824,13 +12828,13 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12881,7 +12885,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -12893,7 +12897,7 @@
         <v>75</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
@@ -12910,10 +12914,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13022,10 +13026,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13136,14 +13140,14 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13165,10 +13169,10 @@
         <v>106</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N98" t="s" s="2">
         <v>109</v>
@@ -13223,7 +13227,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13252,10 +13256,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13281,10 +13285,10 @@
         <v>127</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13335,7 +13339,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -13364,10 +13368,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13390,23 +13394,23 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="R100" t="s" s="2">
         <v>75</v>
@@ -13451,7 +13455,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -13480,10 +13484,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13506,16 +13510,16 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13565,7 +13569,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -13594,10 +13598,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13623,13 +13627,13 @@
         <v>99</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13679,7 +13683,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -13708,10 +13712,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13737,10 +13741,10 @@
         <v>167</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13791,7 +13795,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -13800,7 +13804,7 @@
         <v>76</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>97</v>
@@ -13820,10 +13824,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13849,10 +13853,10 @@
         <v>99</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13903,16 +13907,16 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI104" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>97</v>
@@ -13932,10 +13936,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13961,13 +13965,13 @@
         <v>77</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14017,7 +14021,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14046,10 +14050,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14075,13 +14079,13 @@
         <v>77</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14131,7 +14135,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>

--- a/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
+++ b/ig/improve-doc/StructureDefinition-ans-shareable-valueset.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-02T16:50:25+00:00</t>
+    <t>2024-12-04T07:44:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
